--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>-20.833333333333</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.625</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="L16" s="15">
-        <v>-12.903225806451</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.75</v>
+        <v>-48.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.789473684210</v>
+        <v>-85.238095238095</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
         <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H17" s="15">
-        <v>11.111111111111</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="I17" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J17" s="14">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.054054054054</v>
+        <v>-13.483146067415</v>
       </c>
       <c r="L17" s="15">
-        <v>16.393442622950</v>
+        <v>6.944444444444</v>
       </c>
       <c r="M17" s="15">
-        <v>195.833333333333</v>
+        <v>148.387096774194</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.476190476190</v>
+        <v>-18.947368421052</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>12</v>
+      </c>
+      <c r="G18" s="14">
+        <v>12</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>11</v>
-      </c>
-      <c r="G18" s="14">
-        <v>13</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-15.384615384615</v>
-      </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>57.142857142857</v>
+        <v>38.888888888888</v>
       </c>
       <c r="M18" s="15">
-        <v>-8.333333333333</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.8125</v>
+        <v>-82.993197278911</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-27.272727272727</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F19" s="14">
         <v>42</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>13.513513513513</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I19" s="14">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.836065573770</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.117647058823</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="M19" s="15">
-        <v>17.021276595744</v>
+        <v>36.734693877551</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.327433628318</v>
+        <v>-51.798561151079</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>10.526315789473</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-30</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>40</v>
+        <v>36.842105263157</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.517241379310</v>
+        <v>-84.337349397590</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
+        <v>-18.421052631578</v>
+      </c>
+      <c r="F21" s="17">
+        <v>132</v>
+      </c>
+      <c r="G21" s="17">
+        <v>136</v>
+      </c>
+      <c r="H21" s="18">
         <v>-2.941176470588</v>
       </c>
-      <c r="F21" s="17">
-        <v>143</v>
-      </c>
-      <c r="G21" s="17">
-        <v>139</v>
-      </c>
-      <c r="H21" s="18">
-        <v>2.877697841726</v>
-      </c>
       <c r="I21" s="17">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="J21" s="17">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.225352112676</v>
+        <v>-6.374501992031</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.970873786407</v>
+        <v>-1.260504201680</v>
       </c>
       <c r="M21" s="18">
-        <v>26.708074534161</v>
+        <v>23.684210526315</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.461077844311</v>
+        <v>-69.401041666666</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
+        <v>150</v>
+      </c>
+      <c r="I22" s="14">
+        <v>8</v>
+      </c>
+      <c r="J22" s="14">
+        <v>2</v>
+      </c>
+      <c r="K22" s="15">
         <v>300</v>
-      </c>
-      <c r="I22" s="14">
-        <v>6</v>
-      </c>
-      <c r="J22" s="14">
-        <v>1</v>
-      </c>
-      <c r="K22" s="15">
-        <v>500</v>
       </c>
       <c r="L22" s="15">
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
@@ -1242,16 +1242,16 @@
         <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K23" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L23" s="15">
         <v>-50</v>
       </c>
-      <c r="L23" s="15">
-        <v>-42.857142857142</v>
-      </c>
       <c r="M23" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>20.512820512820</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F24" s="14">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="G24" s="14">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H24" s="15">
-        <v>14.074074074074</v>
+        <v>-4.794520547945</v>
       </c>
       <c r="I24" s="14">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="J24" s="14">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="K24" s="15">
-        <v>9.595959595959</v>
+        <v>5.508474576271</v>
       </c>
       <c r="L24" s="15">
-        <v>24.712643678160</v>
+        <v>18.571428571428</v>
       </c>
       <c r="M24" s="15">
-        <v>99.082568807339</v>
+        <v>99.2</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>3.448275862068</v>
+        <v>-31.25</v>
       </c>
       <c r="F25" s="14">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="G25" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H25" s="15">
-        <v>28.947368421052</v>
+        <v>-2.469135802469</v>
       </c>
       <c r="I25" s="14">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="J25" s="14">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K25" s="15">
-        <v>16.363636363636</v>
+        <v>10.317460317460</v>
       </c>
       <c r="L25" s="15">
-        <v>34.736842105263</v>
+        <v>23.008849557522</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
+        <v>13.333333333333</v>
+      </c>
+      <c r="F26" s="14">
+        <v>63</v>
+      </c>
+      <c r="G26" s="14">
+        <v>62</v>
+      </c>
+      <c r="H26" s="15">
+        <v>1.612903225806</v>
+      </c>
+      <c r="I26" s="14">
+        <v>124</v>
+      </c>
+      <c r="J26" s="14">
+        <v>108</v>
+      </c>
+      <c r="K26" s="15">
+        <v>14.814814814814</v>
+      </c>
+      <c r="L26" s="15">
         <v>0</v>
       </c>
-      <c r="F26" s="14">
-        <v>75</v>
-      </c>
-      <c r="G26" s="14">
-        <v>72</v>
-      </c>
-      <c r="H26" s="15">
-        <v>4.166666666666</v>
-      </c>
-      <c r="I26" s="14">
-        <v>105</v>
-      </c>
-      <c r="J26" s="14">
-        <v>93</v>
-      </c>
-      <c r="K26" s="15">
-        <v>12.903225806451</v>
-      </c>
-      <c r="L26" s="15">
-        <v>9.375</v>
-      </c>
       <c r="M26" s="15">
-        <v>9.375</v>
+        <v>19.230769230769</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>7</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>8</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>250</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="L27" s="15">
-        <v>140</v>
+        <v>116.666666666667</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>500</v>
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="I28" s="14">
+        <v>14</v>
+      </c>
+      <c r="J28" s="14">
         <v>13</v>
       </c>
-      <c r="J28" s="14">
-        <v>8</v>
-      </c>
       <c r="K28" s="15">
-        <v>62.5</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>30</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,73 +860,73 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
+        <v>50</v>
+      </c>
+      <c r="I15" s="14">
+        <v>8</v>
+      </c>
+      <c r="J15" s="14">
+        <v>5</v>
+      </c>
+      <c r="K15" s="15">
+        <v>60</v>
+      </c>
+      <c r="L15" s="15">
         <v>100</v>
       </c>
-      <c r="I15" s="14">
-        <v>9</v>
-      </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
-      <c r="K15" s="15">
-        <v>125</v>
-      </c>
-      <c r="L15" s="15">
-        <v>200</v>
-      </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>9</v>
-      </c>
       <c r="E16" s="15">
-        <v>-55.555555555555</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-25.925925925925</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.390243902439</v>
+        <v>-20</v>
       </c>
       <c r="L16" s="15">
-        <v>-6.060606060606</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.333333333333</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.238095238095</v>
+        <v>-84.680851063829</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-43.75</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.756097560975</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I17" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J17" s="14">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.483146067415</v>
+        <v>-18.095238095238</v>
       </c>
       <c r="L17" s="15">
-        <v>6.944444444444</v>
+        <v>4.878048780487</v>
       </c>
       <c r="M17" s="15">
-        <v>148.387096774194</v>
+        <v>132.432432432432</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.947368421052</v>
+        <v>-21.100917431192</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>4.166666666666</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L18" s="15">
-        <v>38.888888888888</v>
+        <v>30</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.714285714285</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.993197278911</v>
+        <v>-84.971098265896</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>71.428571428571</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>10.526315789473</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="J19" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.470588235294</v>
+        <v>8.108108108108</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.987012987013</v>
+        <v>-12.087912087912</v>
       </c>
       <c r="M19" s="15">
-        <v>36.734693877551</v>
+        <v>35.593220338983</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.798561151079</v>
+        <v>-50.617283950617</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
         <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>13.333333333333</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>8.333333333333</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.714285714285</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>36.842105263157</v>
+        <v>36.363636363636</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.337349397590</v>
+        <v>-84.848484848484</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.421052631578</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G21" s="17">
         <v>136</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.941176470588</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="I21" s="17">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="J21" s="17">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.374501992031</v>
+        <v>-6.315789473684</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.260504201680</v>
+        <v>-1.111111111111</v>
       </c>
       <c r="M21" s="18">
-        <v>23.684210526315</v>
+        <v>20.270270270270</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.401041666666</v>
+        <v>-69.932432432432</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M22" s="15">
         <v>166.666666666667</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M23" s="15">
         <v>-50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-15.789473684210</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G24" s="14">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.794520547945</v>
+        <v>-4.285714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="J24" s="14">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="K24" s="15">
-        <v>5.508474576271</v>
+        <v>4.924242424242</v>
       </c>
       <c r="L24" s="15">
-        <v>18.571428571428</v>
+        <v>16.386554621848</v>
       </c>
       <c r="M24" s="15">
-        <v>99.2</v>
+        <v>95.070422535211</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>12</v>
+      </c>
+      <c r="D25" s="14">
         <v>11</v>
       </c>
-      <c r="D25" s="14">
-        <v>16</v>
-      </c>
       <c r="E25" s="15">
-        <v>-31.25</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F25" s="14">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G25" s="14">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H25" s="15">
-        <v>-2.469135802469</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="I25" s="14">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="J25" s="14">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="K25" s="15">
-        <v>10.317460317460</v>
+        <v>10.218978102189</v>
       </c>
       <c r="L25" s="15">
-        <v>23.008849557522</v>
+        <v>17.054263565891</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>13.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F26" s="14">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H26" s="15">
-        <v>1.612903225806</v>
+        <v>-5.084745762711</v>
       </c>
       <c r="I26" s="14">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="J26" s="14">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>14.814814814814</v>
+        <v>9.917355371900</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-4.316546762589</v>
       </c>
       <c r="M26" s="15">
-        <v>19.230769230769</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>225</v>
+        <v>160</v>
       </c>
       <c r="L27" s="15">
-        <v>116.666666666667</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
+        <v>16</v>
+      </c>
+      <c r="J28" s="14">
         <v>14</v>
       </c>
-      <c r="J28" s="14">
-        <v>13</v>
-      </c>
       <c r="K28" s="15">
-        <v>7.692307692307</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>-90</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,31 +1525,31 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -863,11 +863,11 @@
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -882,7 +882,7 @@
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
         <v>-50</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-4.545454545454</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>-20</v>
+        <v>-18.367346938775</v>
       </c>
       <c r="L16" s="15">
-        <v>-2.702702702702</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.571428571428</v>
+        <v>-48.717948717948</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.680851063829</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-43.75</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G17" s="14">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.529411764705</v>
+        <v>-29.508196721311</v>
       </c>
       <c r="I17" s="14">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="J17" s="14">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.095238095238</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>4.878048780487</v>
+        <v>11.827956989247</v>
       </c>
       <c r="M17" s="15">
-        <v>132.432432432432</v>
+        <v>112.244897959184</v>
       </c>
       <c r="N17" s="15">
-        <v>-21.100917431192</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>22.222222222222</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-3.703703703703</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L18" s="15">
-        <v>30</v>
+        <v>3.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-13.333333333333</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.971098265896</v>
+        <v>-85.353535353535</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>116.666666666667</v>
+        <v>37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>11.111111111111</v>
+        <v>37.5</v>
       </c>
       <c r="I19" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J19" s="14">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K19" s="15">
-        <v>8.108108108108</v>
+        <v>10.975609756097</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.087912087912</v>
+        <v>-12.5</v>
       </c>
       <c r="M19" s="15">
-        <v>35.593220338983</v>
+        <v>42.1875</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.617283950617</v>
+        <v>-50.810810810810</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>26.666666666666</v>
+        <v>31.25</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>7.142857142857</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.666666666666</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M20" s="15">
-        <v>36.363636363636</v>
+        <v>47.826086956521</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.848484848484</v>
+        <v>-84.403669724770</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>13.888888888888</v>
       </c>
       <c r="F21" s="17">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G21" s="17">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.470588235294</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="I21" s="17">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="J21" s="17">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.315789473684</v>
+        <v>-4.049844236760</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.111111111111</v>
+        <v>-2.839116719242</v>
       </c>
       <c r="M21" s="18">
-        <v>20.270270270270</v>
+        <v>20.784313725490</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.932432432432</v>
+        <v>-69.292123629112</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
@@ -1210,7 +1210,7 @@
         <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
         <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L23" s="15">
         <v>-44.444444444444</v>
       </c>
       <c r="M23" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>25</v>
+      </c>
+      <c r="D24" s="14">
         <v>26</v>
       </c>
-      <c r="D24" s="14">
-        <v>28</v>
-      </c>
       <c r="E24" s="15">
-        <v>-7.142857142857</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="F24" s="14">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G24" s="14">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="J24" s="14">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="K24" s="15">
-        <v>4.924242424242</v>
+        <v>3.793103448275</v>
       </c>
       <c r="L24" s="15">
-        <v>16.386554621848</v>
+        <v>4.513888888888</v>
       </c>
       <c r="M24" s="15">
-        <v>95.070422535211</v>
+        <v>88.125</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>9.090909090909</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F25" s="14">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G25" s="14">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H25" s="15">
-        <v>-5.194805194805</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I25" s="14">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="J25" s="14">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="K25" s="15">
-        <v>10.218978102189</v>
+        <v>7.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>17.054263565891</v>
+        <v>2.547770700636</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-30.769230769230</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.084745762711</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="K26" s="15">
-        <v>9.917355371900</v>
+        <v>2.158273381294</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.316546762589</v>
+        <v>-7.189542483660</v>
       </c>
       <c r="M26" s="15">
-        <v>11.764705882352</v>
+        <v>10.9375</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="L27" s="15">
-        <v>85.714285714285</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,22 +1485,22 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>-90</v>
+        <v>-80</v>
       </c>
       <c r="L29" s="15">
+        <v>-71.428571428571</v>
+      </c>
+      <c r="M29" s="15">
+        <v>-81.818181818181</v>
+      </c>
+      <c r="N29" s="15">
         <v>-85.714285714285</v>
-      </c>
-      <c r="M29" s="15">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="N29" s="15">
-        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.909090909090</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -885,45 +885,45 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L15" s="15">
         <v>28.571428571428</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
         <v>-10</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.367346938775</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="L16" s="15">
-        <v>-14.893617021276</v>
+        <v>-22.807017543859</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.717948717948</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.615384615384</v>
+        <v>-84.775086505190</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F17" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G17" s="14">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H17" s="15">
-        <v>-29.508196721311</v>
+        <v>-30</v>
       </c>
       <c r="I17" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J17" s="14">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.333333333333</v>
+        <v>-15.671641791044</v>
       </c>
       <c r="L17" s="15">
-        <v>11.827956989247</v>
+        <v>4.629629629629</v>
       </c>
       <c r="M17" s="15">
-        <v>112.244897959184</v>
+        <v>109.259259259259</v>
       </c>
       <c r="N17" s="15">
-        <v>-20</v>
+        <v>-24.161073825503</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.25</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.121212121212</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="L18" s="15">
-        <v>3.571428571428</v>
+        <v>6.451612903225</v>
       </c>
       <c r="M18" s="15">
-        <v>-19.444444444444</v>
+        <v>-17.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.353535353535</v>
+        <v>-84.651162790697</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>37.5</v>
+        <v>-18.75</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H19" s="15">
-        <v>37.5</v>
+        <v>29.729729729729</v>
       </c>
       <c r="I19" s="14">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J19" s="14">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K19" s="15">
-        <v>10.975609756097</v>
+        <v>6.122448979591</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.5</v>
+        <v>-2.803738317757</v>
       </c>
       <c r="M19" s="15">
-        <v>42.1875</v>
+        <v>50.724637681159</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.810810810810</v>
+        <v>-46.938775510204</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>15</v>
+      </c>
+      <c r="G20" s="14">
+        <v>14</v>
+      </c>
+      <c r="H20" s="15">
+        <v>7.142857142857</v>
+      </c>
+      <c r="I20" s="14">
+        <v>36</v>
+      </c>
+      <c r="J20" s="14">
+        <v>33</v>
+      </c>
+      <c r="K20" s="15">
+        <v>9.090909090909</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-12.195121951219</v>
+      </c>
+      <c r="M20" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="F20" s="14">
-        <v>21</v>
-      </c>
-      <c r="G20" s="14">
-        <v>16</v>
-      </c>
-      <c r="H20" s="15">
-        <v>31.25</v>
-      </c>
-      <c r="I20" s="14">
-        <v>34</v>
-      </c>
-      <c r="J20" s="14">
-        <v>31</v>
-      </c>
-      <c r="K20" s="15">
-        <v>9.677419354838</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-10.526315789473</v>
-      </c>
-      <c r="M20" s="15">
-        <v>47.826086956521</v>
-      </c>
       <c r="N20" s="15">
-        <v>-84.403669724770</v>
+        <v>-85.185185185185</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>13.888888888888</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="F21" s="17">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.816901408450</v>
+        <v>-9.933774834437</v>
       </c>
       <c r="I21" s="17">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="J21" s="17">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.049844236760</v>
+        <v>-6.593406593406</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.839116719242</v>
+        <v>-3.133903133903</v>
       </c>
       <c r="M21" s="18">
-        <v>20.784313725490</v>
+        <v>19.298245614035</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.292123629112</v>
+        <v>-69.230769230769</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1201,16 +1201,16 @@
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L22" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M22" s="15">
         <v>60</v>
-      </c>
-      <c r="M22" s="15">
-        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,22 +1230,22 @@
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-60</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-58.333333333333</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="L23" s="15">
         <v>-44.444444444444</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.846153846153</v>
+        <v>67.647058823529</v>
       </c>
       <c r="F24" s="14">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G24" s="14">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>12.698412698412</v>
       </c>
       <c r="I24" s="14">
-        <v>301</v>
+        <v>359</v>
       </c>
       <c r="J24" s="14">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="K24" s="15">
-        <v>3.793103448275</v>
+        <v>10.802469135802</v>
       </c>
       <c r="L24" s="15">
-        <v>4.513888888888</v>
+        <v>12.539184952978</v>
       </c>
       <c r="M24" s="15">
-        <v>88.125</v>
+        <v>91.978609625668</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.076923076923</v>
+        <v>40</v>
       </c>
       <c r="F25" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G25" s="14">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.695652173913</v>
+        <v>1.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="J25" s="14">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="K25" s="15">
-        <v>7.333333333333</v>
+        <v>11.176470588235</v>
       </c>
       <c r="L25" s="15">
-        <v>2.547770700636</v>
+        <v>7.386363636363</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-44.444444444444</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.285714285714</v>
+        <v>-18.965517241379</v>
       </c>
       <c r="I26" s="14">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="J26" s="14">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="K26" s="15">
-        <v>2.158273381294</v>
+        <v>1.324503311258</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.189542483660</v>
+        <v>-14.044943820224</v>
       </c>
       <c r="M26" s="15">
-        <v>10.9375</v>
+        <v>5.517241379310</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>40</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
         <v>4</v>
       </c>
-      <c r="E28" s="15">
-        <v>-75</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-18.181818181818</v>
+        <v>-30</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
         <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.555555555555</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-22.727272727272</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-84.615384615384</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -882,7 +882,7 @@
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
         <v>-66.666666666666</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
+        <v>10</v>
+      </c>
+      <c r="J15" s="14">
         <v>9</v>
       </c>
-      <c r="J15" s="14">
-        <v>7</v>
-      </c>
       <c r="K15" s="15">
-        <v>28.571428571428</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-19.047619047619</v>
+        <v>20</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J16" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K16" s="15">
-        <v>-16.981132075471</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.807017543859</v>
+        <v>-26.153846153846</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-51.020408163265</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.775086505190</v>
+        <v>-84.905660377358</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
         <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-35.714285714285</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G17" s="14">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" s="15">
-        <v>-30</v>
+        <v>-13.559322033898</v>
       </c>
       <c r="I17" s="14">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="J17" s="14">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.671641791044</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="L17" s="15">
-        <v>4.629629629629</v>
+        <v>9.401709401709</v>
       </c>
       <c r="M17" s="15">
-        <v>109.259259259259</v>
+        <v>116.949152542373</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.161073825503</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-31.25</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K18" s="15">
-        <v>-13.157894736842</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>6.451612903225</v>
+        <v>2.941176470588</v>
       </c>
       <c r="M18" s="15">
-        <v>-17.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.651162790697</v>
+        <v>-84.913793103448</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.75</v>
+        <v>160</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>29.729729729729</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="J19" s="14">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K19" s="15">
-        <v>6.122448979591</v>
+        <v>14.563106796116</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.803738317757</v>
+        <v>-6.349206349206</v>
       </c>
       <c r="M19" s="15">
-        <v>50.724637681159</v>
+        <v>53.246753246753</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.938775510204</v>
+        <v>-43.269230769230</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>7.142857142857</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
+        <v>42</v>
+      </c>
+      <c r="J20" s="14">
         <v>36</v>
       </c>
-      <c r="J20" s="14">
-        <v>33</v>
-      </c>
       <c r="K20" s="15">
-        <v>9.090909090909</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.195121951219</v>
+        <v>-12.5</v>
       </c>
       <c r="M20" s="15">
-        <v>33.333333333333</v>
+        <v>35.483870967741</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.185185185185</v>
+        <v>-84.150943396226</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.255813953488</v>
+        <v>10.810810810810</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.933774834437</v>
+        <v>-2</v>
       </c>
       <c r="I21" s="17">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="J21" s="17">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.593406593406</v>
+        <v>-4.738154613466</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.133903133903</v>
+        <v>-3.778337531486</v>
       </c>
       <c r="M21" s="18">
-        <v>19.298245614035</v>
+        <v>21.269841269841</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.230769230769</v>
+        <v>-68.086883876357</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,29 +1188,29 @@
       <c r="E22" s="15">
         <v>-100</v>
       </c>
-      <c r="F22" s="14">
-        <v>2</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-83.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23" s="14">
         <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-64.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-44.444444444444</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M23" s="15">
-        <v>-54.545454545454</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E24" s="15">
-        <v>67.647058823529</v>
+        <v>-11.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="G24" s="14">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="H24" s="15">
-        <v>12.698412698412</v>
+        <v>6.756756756756</v>
       </c>
       <c r="I24" s="14">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="J24" s="14">
-        <v>324</v>
+        <v>384</v>
       </c>
       <c r="K24" s="15">
-        <v>10.802469135802</v>
+        <v>6.25</v>
       </c>
       <c r="L24" s="15">
-        <v>12.539184952978</v>
+        <v>19.298245614035</v>
       </c>
       <c r="M24" s="15">
-        <v>91.978609625668</v>
+        <v>99.024390243902</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="E25" s="15">
-        <v>40</v>
+        <v>-36.170212765957</v>
       </c>
       <c r="F25" s="14">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="H25" s="15">
-        <v>1.666666666666</v>
+        <v>-12.087912087912</v>
       </c>
       <c r="I25" s="14">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="J25" s="14">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="K25" s="15">
-        <v>11.176470588235</v>
+        <v>0.921658986175</v>
       </c>
       <c r="L25" s="15">
-        <v>7.386363636363</v>
+        <v>12.307692307692</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>113.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G26" s="14">
         <v>58</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.965517241379</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I26" s="14">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="J26" s="14">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="K26" s="15">
-        <v>1.324503311258</v>
+        <v>11.445783132530</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.044943820224</v>
+        <v>-6.565656565656</v>
       </c>
       <c r="M26" s="15">
-        <v>5.517241379310</v>
+        <v>11.445783132530</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-30</v>
+        <v>12.5</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>-8.695652173913</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-71.428571428571</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.818181818181</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-87.5</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-60</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.666666666666</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,14 +1625,14 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -878,55 +878,55 @@
       <c r="K14" s="15">
         <v>0</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>42.857142857142</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-9.090909090909</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F16" s="14">
+        <v>19</v>
+      </c>
+      <c r="G16" s="14">
         <v>18</v>
       </c>
-      <c r="G16" s="14">
-        <v>15</v>
-      </c>
       <c r="H16" s="15">
-        <v>20</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K16" s="15">
         <v>-14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.153846153846</v>
+        <v>-19.402985074626</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.020408163265</v>
+        <v>-49.532710280373</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.905660377358</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>14.285714285714</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G17" s="14">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.559322033898</v>
+        <v>18.867924528301</v>
       </c>
       <c r="I17" s="14">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="J17" s="14">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.513513513513</v>
+        <v>-5.063291139240</v>
       </c>
       <c r="L17" s="15">
-        <v>9.401709401709</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M17" s="15">
-        <v>116.949152542373</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N17" s="15">
-        <v>-20</v>
+        <v>-13.793103448275</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>10</v>
-      </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-58.333333333333</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.083333333333</v>
+        <v>-22</v>
       </c>
       <c r="L18" s="15">
-        <v>2.941176470588</v>
+        <v>11.428571428571</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.913793103448</v>
+        <v>-84.016393442623</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>160</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>42.857142857142</v>
+        <v>12.820512820512</v>
       </c>
       <c r="I19" s="14">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J19" s="14">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K19" s="15">
-        <v>14.563106796116</v>
+        <v>10.619469026548</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.349206349206</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M19" s="15">
-        <v>53.246753246753</v>
+        <v>50.602409638554</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.269230769230</v>
+        <v>-45.175438596491</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>66.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I20" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K20" s="15">
-        <v>16.666666666666</v>
+        <v>4.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.5</v>
+        <v>-14.545454545454</v>
       </c>
       <c r="M20" s="15">
-        <v>35.483870967741</v>
+        <v>34.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.150943396226</v>
+        <v>-83.623693379790</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>10.810810810810</v>
+        <v>7.894736842105</v>
       </c>
       <c r="F21" s="17">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G21" s="17">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H21" s="18">
-        <v>-2</v>
+        <v>1.298701298701</v>
       </c>
       <c r="I21" s="17">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="J21" s="17">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.738154613466</v>
+        <v>-3.189066059225</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.778337531486</v>
+        <v>-2.298850574712</v>
       </c>
       <c r="M21" s="18">
-        <v>21.269841269841</v>
+        <v>19.718309859154</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.086883876357</v>
+        <v>-67.332820906994</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
         <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,25 +1233,25 @@
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
         <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>-36.363636363636</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D24" s="14">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.666666666666</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="F24" s="14">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="G24" s="14">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="H24" s="15">
-        <v>6.756756756756</v>
+        <v>6.707317073170</v>
       </c>
       <c r="I24" s="14">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="J24" s="14">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="K24" s="15">
-        <v>6.25</v>
+        <v>5.373831775700</v>
       </c>
       <c r="L24" s="15">
-        <v>19.298245614035</v>
+        <v>23.561643835616</v>
       </c>
       <c r="M24" s="15">
-        <v>99.024390243902</v>
+        <v>91.101694915254</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D25" s="14">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.170212765957</v>
+        <v>22.727272727272</v>
       </c>
       <c r="F25" s="14">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="G25" s="14">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.087912087912</v>
+        <v>-6.862745098039</v>
       </c>
       <c r="I25" s="14">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="J25" s="14">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="K25" s="15">
-        <v>0.921658986175</v>
+        <v>2.928870292887</v>
       </c>
       <c r="L25" s="15">
-        <v>12.307692307692</v>
+        <v>18.840579710144</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>113.333333333333</v>
+        <v>125</v>
       </c>
       <c r="F26" s="14">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G26" s="14">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H26" s="15">
-        <v>6.896551724137</v>
+        <v>39.622641509434</v>
       </c>
       <c r="I26" s="14">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="J26" s="14">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K26" s="15">
-        <v>11.445783132530</v>
+        <v>18.390804597701</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.565656565656</v>
+        <v>-3.738317757009</v>
       </c>
       <c r="M26" s="15">
-        <v>11.445783132530</v>
+        <v>7.291666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>36.363636363636</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
+        <v>11</v>
+      </c>
+      <c r="G28" s="14">
         <v>9</v>
       </c>
-      <c r="G28" s="14">
-        <v>8</v>
-      </c>
       <c r="H28" s="15">
-        <v>12.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1494,13 +1494,13 @@
         <v>-80</v>
       </c>
       <c r="L29" s="15">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M29" s="15">
         <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.235294117647</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M30" s="15">
         <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -890,16 +890,16 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -911,22 +911,22 @@
         <v>-75</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
         <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>5.555555555555</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I16" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J16" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.285714285714</v>
+        <v>-11.940298507462</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.402985074626</v>
+        <v>-20.270270270270</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.532710280373</v>
+        <v>-51.639344262295</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.615384615384</v>
+        <v>-84.350132625994</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
         <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H17" s="15">
-        <v>18.867924528301</v>
+        <v>31.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="J17" s="14">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.063291139240</v>
+        <v>-0.606060606060</v>
       </c>
       <c r="L17" s="15">
-        <v>15.384615384615</v>
+        <v>11.564625850340</v>
       </c>
       <c r="M17" s="15">
-        <v>114.285714285714</v>
+        <v>115.789473684211</v>
       </c>
       <c r="N17" s="15">
-        <v>-13.793103448275</v>
+        <v>-19.607843137254</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>6</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-43.478260869565</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I18" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K18" s="15">
-        <v>-22</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L18" s="15">
-        <v>11.428571428571</v>
+        <v>15</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.016393442623</v>
+        <v>-82.375478927203</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F19" s="14">
+        <v>41</v>
+      </c>
+      <c r="G19" s="14">
         <v>44</v>
       </c>
-      <c r="G19" s="14">
-        <v>39</v>
-      </c>
       <c r="H19" s="15">
-        <v>12.820512820512</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="I19" s="14">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="K19" s="15">
-        <v>10.619469026548</v>
+        <v>6.349206349206</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.714285714285</v>
+        <v>-14.649681528662</v>
       </c>
       <c r="M19" s="15">
-        <v>50.602409638554</v>
+        <v>39.583333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.175438596491</v>
+        <v>-48.062015503876</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
         <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.882352941176</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I20" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J20" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K20" s="15">
-        <v>4.444444444444</v>
+        <v>2.083333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-14.545454545454</v>
+        <v>-12.5</v>
       </c>
       <c r="M20" s="15">
-        <v>34.285714285714</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.623693379790</v>
+        <v>-84.6875</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>7.894736842105</v>
+        <v>18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G21" s="17">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H21" s="18">
-        <v>1.298701298701</v>
+        <v>1.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="J21" s="17">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.189066059225</v>
+        <v>-1.698513800424</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.298850574712</v>
+        <v>-3.941908713692</v>
       </c>
       <c r="M21" s="18">
-        <v>19.718309859154</v>
+        <v>16.331658291457</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.332820906994</v>
+        <v>-67.824878387769</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="15">
         <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>150</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23" s="14">
         <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.111111111111</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>-27.272727272727</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D24" s="14">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.545454545454</v>
+        <v>59.459459459459</v>
       </c>
       <c r="F24" s="14">
+        <v>212</v>
+      </c>
+      <c r="G24" s="14">
         <v>175</v>
       </c>
-      <c r="G24" s="14">
-        <v>164</v>
-      </c>
       <c r="H24" s="15">
-        <v>6.707317073170</v>
+        <v>21.142857142857</v>
       </c>
       <c r="I24" s="14">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="J24" s="14">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="K24" s="15">
-        <v>5.373831775700</v>
+        <v>9.892473118279</v>
       </c>
       <c r="L24" s="15">
-        <v>23.561643835616</v>
+        <v>28.070175438596</v>
       </c>
       <c r="M24" s="15">
-        <v>91.101694915254</v>
+        <v>97.297297297297</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>22.727272727272</v>
+        <v>29.166666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="G25" s="14">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="H25" s="15">
-        <v>-6.862745098039</v>
+        <v>2.654867256637</v>
       </c>
       <c r="I25" s="14">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="J25" s="14">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="K25" s="15">
-        <v>2.928870292887</v>
+        <v>5.323193916349</v>
       </c>
       <c r="L25" s="15">
-        <v>18.840579710144</v>
+        <v>21.491228070175</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>125</v>
+        <v>228.571428571429</v>
       </c>
       <c r="F26" s="14">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G26" s="14">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>39.622641509434</v>
+        <v>109.52380952381</v>
       </c>
       <c r="I26" s="14">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="J26" s="14">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="K26" s="15">
-        <v>18.390804597701</v>
+        <v>27.624309392265</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.738317757009</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>7.291666666666</v>
+        <v>14.356435643564</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>55.555555555555</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>27.272727272727</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
         <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
+        <v>29</v>
+      </c>
+      <c r="J28" s="14">
         <v>27</v>
       </c>
-      <c r="J28" s="14">
-        <v>23</v>
-      </c>
       <c r="K28" s="15">
-        <v>17.391304347826</v>
+        <v>7.407407407407</v>
       </c>
       <c r="L28" s="15">
-        <v>3.846153846153</v>
+        <v>7.407407407407</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="L29" s="15">
         <v>-77.777777777777</v>
@@ -1500,7 +1500,7 @@
         <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>-71.428571428571</v>
@@ -1541,7 +1541,7 @@
         <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1635,13 +1635,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
@@ -899,34 +899,34 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>11.111111111111</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L15" s="15">
-        <v>42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N15" s="15">
-        <v>-28.571428571428</v>
+        <v>-26.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
         <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>11.111111111111</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J16" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.940298507462</v>
+        <v>-8.450704225352</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.270270270270</v>
+        <v>-17.721518987341</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.639344262295</v>
+        <v>-48.818897637795</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.350132625994</v>
+        <v>-83.910891089108</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>63.636363636363</v>
       </c>
       <c r="F17" s="14">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>31.111111111111</v>
+        <v>64.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="J17" s="14">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.606060606060</v>
+        <v>3.409090909090</v>
       </c>
       <c r="L17" s="15">
-        <v>11.564625850340</v>
+        <v>15.923566878980</v>
       </c>
       <c r="M17" s="15">
-        <v>115.789473684211</v>
+        <v>111.627906976744</v>
       </c>
       <c r="N17" s="15">
-        <v>-19.607843137254</v>
+        <v>-18.385650224215</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.047619047619</v>
+        <v>-5</v>
       </c>
       <c r="I18" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.814814814814</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L18" s="15">
-        <v>15</v>
+        <v>15.555555555555</v>
       </c>
       <c r="M18" s="15">
-        <v>-14.814814814814</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.375478927203</v>
+        <v>-81.362007168458</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-23.076923076923</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.818181818181</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I19" s="14">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="J19" s="14">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K19" s="15">
-        <v>6.349206349206</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.649681528662</v>
+        <v>-13.772455089820</v>
       </c>
       <c r="M19" s="15">
-        <v>39.583333333333</v>
+        <v>38.461538461538</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.062015503876</v>
+        <v>-48.571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>-17.647058823529</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I20" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J20" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K20" s="15">
-        <v>2.083333333333</v>
+        <v>3.921568627450</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.5</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="M20" s="15">
-        <v>16.666666666666</v>
+        <v>6</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.6875</v>
+        <v>-85.154061624649</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>18.75</v>
+        <v>67.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G21" s="17">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="H21" s="18">
-        <v>1.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I21" s="17">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="J21" s="17">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.698513800424</v>
+        <v>1.803607214428</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.941908713692</v>
+        <v>-1.550387596899</v>
       </c>
       <c r="M21" s="18">
-        <v>16.331658291457</v>
+        <v>17.321016166281</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.824878387769</v>
+        <v>-67.498400511836</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1201,19 +1201,19 @@
         <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M22" s="15">
         <v>28.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>100</v>
+      </c>
+      <c r="F23" s="14">
+        <v>7</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>600</v>
+      </c>
+      <c r="I23" s="14">
+        <v>12</v>
+      </c>
+      <c r="J23" s="14">
+        <v>15</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-20</v>
+      </c>
+      <c r="L23" s="15">
         <v>20</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="14">
-        <v>5</v>
-      </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
-      <c r="H23" s="15">
-        <v>150</v>
-      </c>
-      <c r="I23" s="14">
-        <v>10</v>
-      </c>
-      <c r="J23" s="14">
-        <v>14</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="L23" s="15">
-        <v>11.111111111111</v>
-      </c>
       <c r="M23" s="15">
-        <v>-16.666666666666</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>59.459459459459</v>
+        <v>160.606060606061</v>
       </c>
       <c r="F24" s="14">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="G24" s="14">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H24" s="15">
-        <v>21.142857142857</v>
+        <v>39.080459770114</v>
       </c>
       <c r="I24" s="14">
-        <v>511</v>
+        <v>598</v>
       </c>
       <c r="J24" s="14">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="K24" s="15">
-        <v>9.892473118279</v>
+        <v>20.080321285140</v>
       </c>
       <c r="L24" s="15">
-        <v>28.070175438596</v>
+        <v>37.471264367816</v>
       </c>
       <c r="M24" s="15">
-        <v>97.297297297297</v>
+        <v>108.362369337979</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>29.166666666666</v>
+        <v>216.666666666667</v>
       </c>
       <c r="F25" s="14">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="G25" s="14">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H25" s="15">
-        <v>2.654867256637</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="J25" s="14">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="K25" s="15">
-        <v>5.323193916349</v>
+        <v>19.928825622775</v>
       </c>
       <c r="L25" s="15">
-        <v>21.491228070175</v>
+        <v>33.730158730158</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>228.571428571429</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F26" s="14">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>109.52380952381</v>
+        <v>93.877551020408</v>
       </c>
       <c r="I26" s="14">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="J26" s="14">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="K26" s="15">
-        <v>27.624309392265</v>
+        <v>24</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-1.976284584980</v>
       </c>
       <c r="M26" s="15">
-        <v>14.356435643564</v>
+        <v>10.714285714285</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>111.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>63.636363636363</v>
+        <v>46.153846153846</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>4</v>
       </c>
       <c r="E28" s="15">
         <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="14">
+        <v>30</v>
+      </c>
+      <c r="J28" s="14">
         <v>29</v>
       </c>
-      <c r="J28" s="14">
-        <v>27</v>
-      </c>
       <c r="K28" s="15">
-        <v>7.407407407407</v>
+        <v>3.448275862068</v>
       </c>
       <c r="L28" s="15">
-        <v>7.407407407407</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1635,13 +1635,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>60</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="L15" s="15">
         <v>37.5</v>
@@ -926,7 +926,7 @@
         <v>120</v>
       </c>
       <c r="N15" s="15">
-        <v>-26.666666666666</v>
+        <v>-35.294117647058</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>16.666666666666</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J16" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.450704225352</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.721518987341</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.818897637795</v>
+        <v>-49.640287769784</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.910891089108</v>
+        <v>-83.644859813084</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>63.636363636363</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H17" s="15">
-        <v>64.285714285714</v>
+        <v>58.139534883720</v>
       </c>
       <c r="I17" s="14">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J17" s="14">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="K17" s="15">
-        <v>3.409090909090</v>
+        <v>3.664921465968</v>
       </c>
       <c r="L17" s="15">
-        <v>15.923566878980</v>
+        <v>12.5</v>
       </c>
       <c r="M17" s="15">
-        <v>111.627906976744</v>
+        <v>125</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.385650224215</v>
+        <v>-18.518518518518</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-5</v>
+        <v>53.846153846153</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J18" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.344827586206</v>
+        <v>-9.836065573770</v>
       </c>
       <c r="L18" s="15">
-        <v>15.555555555555</v>
+        <v>17.021276595744</v>
       </c>
       <c r="M18" s="15">
-        <v>-10.344827586206</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.362007168458</v>
+        <v>-81.099656357388</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>83.333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H19" s="15">
-        <v>11.764705882352</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="I19" s="14">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="J19" s="14">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K19" s="15">
-        <v>9.090909090909</v>
+        <v>10</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.772455089820</v>
+        <v>-12.5</v>
       </c>
       <c r="M19" s="15">
-        <v>38.461538461538</v>
+        <v>41.284403669724</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.571428571428</v>
+        <v>-48.322147651006</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
         <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>-11.111111111111</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J20" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K20" s="15">
-        <v>3.921568627450</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.169491525423</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="M20" s="15">
-        <v>6</v>
+        <v>3.846153846153</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.154061624649</v>
+        <v>-85.561497326203</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>67.857142857142</v>
+        <v>2.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G21" s="17">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H21" s="18">
-        <v>22.222222222222</v>
+        <v>19.548872180451</v>
       </c>
       <c r="I21" s="17">
-        <v>508</v>
+        <v>543</v>
       </c>
       <c r="J21" s="17">
-        <v>499</v>
+        <v>534</v>
       </c>
       <c r="K21" s="18">
-        <v>1.803607214428</v>
+        <v>1.685393258426</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.550387596899</v>
+        <v>-1.985559566787</v>
       </c>
       <c r="M21" s="18">
-        <v>17.321016166281</v>
+        <v>19.340659340659</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.498400511836</v>
+        <v>-67.210144927536</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L22" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M22" s="15">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-18.75</v>
       </c>
       <c r="L23" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M23" s="15">
-        <v>-7.692307692307</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>160.606060606061</v>
+        <v>63.157894736842</v>
       </c>
       <c r="F24" s="14">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="G24" s="14">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="H24" s="15">
-        <v>39.080459770114</v>
+        <v>63.909774436090</v>
       </c>
       <c r="I24" s="14">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="J24" s="14">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="K24" s="15">
-        <v>20.080321285140</v>
+        <v>21.470019342359</v>
       </c>
       <c r="L24" s="15">
-        <v>37.471264367816</v>
+        <v>31.106471816283</v>
       </c>
       <c r="M24" s="15">
-        <v>108.362369337979</v>
+        <v>104.560260586319</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>216.666666666667</v>
+        <v>162.5</v>
       </c>
       <c r="F25" s="14">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="G25" s="14">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="H25" s="15">
-        <v>33.333333333333</v>
+        <v>93.055555555555</v>
       </c>
       <c r="I25" s="14">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="J25" s="14">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="K25" s="15">
-        <v>19.928825622775</v>
+        <v>23.875432525951</v>
       </c>
       <c r="L25" s="15">
-        <v>33.730158730158</v>
+        <v>33.085501858736</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.789473684210</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>93.877551020408</v>
+        <v>53.846153846153</v>
       </c>
       <c r="I26" s="14">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="J26" s="14">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="K26" s="15">
-        <v>24</v>
+        <v>22.935779816513</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.976284584980</v>
+        <v>1.132075471698</v>
       </c>
       <c r="M26" s="15">
-        <v>10.714285714285</v>
+        <v>14.042553191489</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="I27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>111.111111111111</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>46.153846153846</v>
+        <v>53.846153846153</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>9</v>
       </c>
-      <c r="G28" s="14">
-        <v>11</v>
-      </c>
       <c r="H28" s="15">
-        <v>-18.181818181818</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K28" s="15">
-        <v>3.448275862068</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>7.142857142857</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-77.777777777777</v>
       </c>
       <c r="M29" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.548387096774</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-71.428571428571</v>
       </c>
       <c r="M30" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -882,51 +882,51 @@
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>10</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>120</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-35.294117647058</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>10</v>
+        <v>43.75</v>
       </c>
       <c r="I16" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J16" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.894736842105</v>
+        <v>-2.531645569620</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M16" s="15">
-        <v>-49.640287769784</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.644859813084</v>
+        <v>-82.774049217002</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G17" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>58.139534883720</v>
+        <v>54.761904761904</v>
       </c>
       <c r="I17" s="14">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="J17" s="14">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K17" s="15">
-        <v>3.664921465968</v>
+        <v>8</v>
       </c>
       <c r="L17" s="15">
-        <v>12.5</v>
+        <v>11.340206185567</v>
       </c>
       <c r="M17" s="15">
-        <v>125</v>
+        <v>127.368421052632</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.518518518518</v>
+        <v>-14.624505928853</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>53.846153846153</v>
+        <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J18" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K18" s="15">
-        <v>-9.836065573770</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L18" s="15">
-        <v>17.021276595744</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-6.779661016949</v>
+        <v>-4.477611940298</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.099656357388</v>
+        <v>-79.874213836478</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>37.5</v>
+        <v>366.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.405405405405</v>
+        <v>36.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="J19" s="14">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K19" s="15">
-        <v>10</v>
+        <v>16.783216783216</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.5</v>
+        <v>-10.215053763440</v>
       </c>
       <c r="M19" s="15">
-        <v>41.284403669724</v>
+        <v>45.217391304347</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.322147651006</v>
+        <v>-49.546827794561</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J20" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.903225806451</v>
+        <v>-10.606060606060</v>
       </c>
       <c r="M20" s="15">
-        <v>3.846153846153</v>
+        <v>3.508771929824</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.561497326203</v>
+        <v>-85.175879396984</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>2.857142857142</v>
+        <v>129.166666666667</v>
       </c>
       <c r="F21" s="17">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G21" s="17">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="H21" s="18">
-        <v>19.548872180451</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>543</v>
+        <v>598</v>
       </c>
       <c r="J21" s="17">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="K21" s="18">
-        <v>1.685393258426</v>
+        <v>7.168458781362</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.985559566787</v>
+        <v>0.673400673400</v>
       </c>
       <c r="M21" s="18">
-        <v>19.340659340659</v>
+        <v>22.792607802874</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.210144927536</v>
+        <v>-66.309859154929</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
+        <v>11</v>
+      </c>
+      <c r="J22" s="14">
         <v>10</v>
       </c>
-      <c r="J22" s="14">
-        <v>9</v>
-      </c>
       <c r="K22" s="15">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="L22" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>13</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L23" s="15">
-        <v>30</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M23" s="15">
-        <v>-7.142857142857</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E24" s="15">
-        <v>63.157894736842</v>
+        <v>-14</v>
       </c>
       <c r="F24" s="14">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G24" s="14">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H24" s="15">
-        <v>63.909774436090</v>
+        <v>58.273381294964</v>
       </c>
       <c r="I24" s="14">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="J24" s="14">
-        <v>517</v>
+        <v>567</v>
       </c>
       <c r="K24" s="15">
-        <v>21.470019342359</v>
+        <v>18.518518518518</v>
       </c>
       <c r="L24" s="15">
-        <v>31.106471816283</v>
+        <v>24.675324675324</v>
       </c>
       <c r="M24" s="15">
-        <v>104.560260586319</v>
+        <v>100.597014925373</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>162.5</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G25" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H25" s="15">
-        <v>93.055555555555</v>
+        <v>78.481012658227</v>
       </c>
       <c r="I25" s="14">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="J25" s="14">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="K25" s="15">
-        <v>23.875432525951</v>
+        <v>21.698113207547</v>
       </c>
       <c r="L25" s="15">
-        <v>33.085501858736</v>
+        <v>28.145695364238</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="F26" s="14">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H26" s="15">
-        <v>53.846153846153</v>
+        <v>40</v>
       </c>
       <c r="I26" s="14">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="J26" s="14">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="K26" s="15">
-        <v>22.935779816513</v>
+        <v>24.786324786324</v>
       </c>
       <c r="L26" s="15">
-        <v>1.132075471698</v>
+        <v>3.914590747330</v>
       </c>
       <c r="M26" s="15">
-        <v>14.042553191489</v>
+        <v>18.699186991869</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>500</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>91.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>53.846153846153</v>
+        <v>76.923076923076</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J28" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-3.225806451612</v>
+        <v>9.375</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>-81.818181818181</v>
       </c>
       <c r="L29" s="15">
-        <v>-77.777777777777</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.75</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.103448275862</v>
+        <v>-94.594594594594</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>14</v>
@@ -926,7 +926,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-30</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>43.75</v>
+        <v>64.705882352941</v>
       </c>
       <c r="I16" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J16" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.531645569620</v>
+        <v>2.380952380952</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.384615384615</v>
+        <v>-18.867924528301</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.153846153846</v>
+        <v>-43.046357615894</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.774049217002</v>
+        <v>-81.856540084388</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>111.111111111111</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F17" s="14">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>54.761904761904</v>
+        <v>18.867924528301</v>
       </c>
       <c r="I17" s="14">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="J17" s="14">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="K17" s="15">
-        <v>8</v>
+        <v>5.045871559633</v>
       </c>
       <c r="L17" s="15">
-        <v>11.340206185567</v>
+        <v>10.628019323671</v>
       </c>
       <c r="M17" s="15">
-        <v>127.368421052632</v>
+        <v>131.313131313131</v>
       </c>
       <c r="N17" s="15">
-        <v>-14.624505928853</v>
+        <v>-15.185185185185</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>800</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
         <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I18" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J18" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K18" s="15">
-        <v>3.225806451612</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>33.333333333333</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M18" s="15">
-        <v>-4.477611940298</v>
+        <v>-9.589041095890</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.874213836478</v>
+        <v>-80.701754385964</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>366.666666666667</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>36.666666666666</v>
+        <v>74.074074074074</v>
       </c>
       <c r="I19" s="14">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="J19" s="14">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="K19" s="15">
-        <v>16.783216783216</v>
+        <v>18.954248366013</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.215053763440</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M19" s="15">
-        <v>45.217391304347</v>
+        <v>50.413223140495</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.546827794561</v>
+        <v>-49.303621169916</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-16.666666666666</v>
+        <v>250</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I20" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J20" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.666666666666</v>
+        <v>6.451612903225</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.606060606060</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="M20" s="15">
-        <v>3.508771929824</v>
+        <v>6.451612903225</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.175879396984</v>
+        <v>-84.397163120567</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E21" s="18">
-        <v>129.166666666667</v>
+        <v>20.512820512820</v>
       </c>
       <c r="F21" s="17">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G21" s="17">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H21" s="18">
         <v>42.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>598</v>
+        <v>644</v>
       </c>
       <c r="J21" s="17">
-        <v>558</v>
+        <v>597</v>
       </c>
       <c r="K21" s="18">
-        <v>7.168458781362</v>
+        <v>7.872696817420</v>
       </c>
       <c r="L21" s="18">
-        <v>0.673400673400</v>
+        <v>0.940438871473</v>
       </c>
       <c r="M21" s="18">
-        <v>22.792607802874</v>
+        <v>24.806201550387</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.309859154929</v>
+        <v>-66.069546891464</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
+        <v>13</v>
+      </c>
+      <c r="J22" s="14">
         <v>11</v>
       </c>
-      <c r="J22" s="14">
-        <v>10</v>
-      </c>
       <c r="K22" s="15">
-        <v>10</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L22" s="15">
-        <v>57.142857142857</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M22" s="15">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>13</v>
@@ -1248,7 +1248,7 @@
         <v>-23.529411764705</v>
       </c>
       <c r="L23" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M23" s="15">
         <v>-13.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E24" s="15">
-        <v>-14</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="G24" s="14">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H24" s="15">
-        <v>58.273381294964</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>672</v>
+        <v>702</v>
       </c>
       <c r="J24" s="14">
-        <v>567</v>
+        <v>615</v>
       </c>
       <c r="K24" s="15">
-        <v>18.518518518518</v>
+        <v>14.146341463414</v>
       </c>
       <c r="L24" s="15">
-        <v>24.675324675324</v>
+        <v>23.809523809523</v>
       </c>
       <c r="M24" s="15">
-        <v>100.597014925373</v>
+        <v>92.857142857142</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14">
         <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F25" s="14">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G25" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>78.481012658227</v>
+        <v>54.761904761904</v>
       </c>
       <c r="I25" s="14">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="J25" s="14">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="K25" s="15">
-        <v>21.698113207547</v>
+        <v>18.155619596541</v>
       </c>
       <c r="L25" s="15">
-        <v>28.145695364238</v>
+        <v>26.543209876543</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>43.75</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F26" s="14">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G26" s="14">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>40</v>
+        <v>-1.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="J26" s="14">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="K26" s="15">
-        <v>24.786324786324</v>
+        <v>19.53125</v>
       </c>
       <c r="L26" s="15">
-        <v>3.914590747330</v>
+        <v>3.378378378378</v>
       </c>
       <c r="M26" s="15">
-        <v>18.699186991869</v>
+        <v>17.241379310344</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>23</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="I28" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="L28" s="15">
-        <v>9.375</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1500,7 +1500,7 @@
         <v>-86.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-95</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1541,7 +1541,7 @@
         <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.594594594594</v>
+        <v>-95.121951219512</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -885,48 +885,48 @@
         <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>4</v>
       </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>-36.363636363636</v>
+        <v>-31.818181818181</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>80</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F16" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>64.705882352941</v>
+        <v>25</v>
       </c>
       <c r="I16" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J16" s="14">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K16" s="15">
-        <v>2.380952380952</v>
+        <v>-1.052631578947</v>
       </c>
       <c r="L16" s="15">
-        <v>-18.867924528301</v>
+        <v>-19.658119658119</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.046357615894</v>
+        <v>-39.743589743589</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.856540084388</v>
+        <v>-81.386138613861</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-27.777777777777</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H17" s="15">
-        <v>18.867924528301</v>
+        <v>5.084745762711</v>
       </c>
       <c r="I17" s="14">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="J17" s="14">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="K17" s="15">
-        <v>5.045871559633</v>
+        <v>5.106382978723</v>
       </c>
       <c r="L17" s="15">
-        <v>10.628019323671</v>
+        <v>12.785388127853</v>
       </c>
       <c r="M17" s="15">
-        <v>131.313131313131</v>
+        <v>147</v>
       </c>
       <c r="N17" s="15">
-        <v>-15.185185185185</v>
+        <v>-11.785714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>75</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I18" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J18" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="L18" s="15">
-        <v>29.411764705882</v>
+        <v>23.214285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-9.589041095890</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.701754385964</v>
+        <v>-80.886426592797</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>74.074074074074</v>
+        <v>48.484848484848</v>
       </c>
       <c r="I19" s="14">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="J19" s="14">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="K19" s="15">
-        <v>18.954248366013</v>
+        <v>17.575757575757</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.142857142857</v>
+        <v>-7.177033492822</v>
       </c>
       <c r="M19" s="15">
-        <v>50.413223140495</v>
+        <v>56.451612903225</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.303621169916</v>
+        <v>-50.510204081632</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,13 +1098,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>250</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
         <v>17</v>
@@ -1116,22 +1116,22 @@
         <v>21.428571428571</v>
       </c>
       <c r="I20" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J20" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K20" s="15">
-        <v>6.451612903225</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L20" s="15">
-        <v>-4.347826086956</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="M20" s="15">
-        <v>6.451612903225</v>
+        <v>12.903225806451</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.397163120567</v>
+        <v>-84.162895927601</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>20.512820512820</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="F21" s="17">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G21" s="17">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="H21" s="18">
-        <v>42.857142857142</v>
+        <v>21.088435374149</v>
       </c>
       <c r="I21" s="17">
-        <v>644</v>
+        <v>690</v>
       </c>
       <c r="J21" s="17">
-        <v>597</v>
+        <v>646</v>
       </c>
       <c r="K21" s="18">
-        <v>7.872696817420</v>
+        <v>6.811145510835</v>
       </c>
       <c r="L21" s="18">
-        <v>0.940438871473</v>
+        <v>1.173020527859</v>
       </c>
       <c r="M21" s="18">
-        <v>24.806201550387</v>
+        <v>28.491620111731</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.069546891464</v>
+        <v>-65.705765407554</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>18.181818181818</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L22" s="15">
-        <v>85.714285714285</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="15">
-        <v>-23.529411764705</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L23" s="15">
-        <v>8.333333333333</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M23" s="15">
-        <v>-13.333333333333</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.5</v>
+        <v>32.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>190</v>
+        <v>142</v>
       </c>
       <c r="G24" s="14">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H24" s="15">
-        <v>26.666666666666</v>
+        <v>-2.068965517241</v>
       </c>
       <c r="I24" s="14">
-        <v>702</v>
+        <v>739</v>
       </c>
       <c r="J24" s="14">
-        <v>615</v>
+        <v>643</v>
       </c>
       <c r="K24" s="15">
-        <v>14.146341463414</v>
+        <v>14.930015552099</v>
       </c>
       <c r="L24" s="15">
-        <v>23.809523809523</v>
+        <v>23.166666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>92.857142857142</v>
+        <v>89.487179487179</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-20.689655172413</v>
+        <v>46.153846153846</v>
       </c>
       <c r="F25" s="14">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H25" s="15">
-        <v>54.761904761904</v>
+        <v>16.455696202531</v>
       </c>
       <c r="I25" s="14">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="J25" s="14">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="K25" s="15">
-        <v>18.155619596541</v>
+        <v>19.166666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>26.543209876543</v>
+        <v>23.988439306358</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.363636363636</v>
+        <v>-36</v>
       </c>
       <c r="F26" s="14">
         <v>74</v>
       </c>
       <c r="G26" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.333333333333</v>
+        <v>-8.641975308641</v>
       </c>
       <c r="I26" s="14">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="J26" s="14">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="K26" s="15">
-        <v>19.53125</v>
+        <v>15.302491103202</v>
       </c>
       <c r="L26" s="15">
-        <v>3.378378378378</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>17.241379310344</v>
+        <v>18.681318681318</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>91.666666666666</v>
+        <v>84.615384615384</v>
       </c>
       <c r="L27" s="15">
-        <v>76.923076923076</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="I28" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J28" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K28" s="15">
-        <v>-2.702702702702</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>12.5</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-81.818181818181</v>
+        <v>-75</v>
       </c>
       <c r="L29" s="15">
-        <v>-83.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="M29" s="15">
-        <v>-86.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.454545454545</v>
+        <v>-93.617021276595</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-77.777777777777</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-77.777777777777</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.121951219512</v>
+        <v>-93.181818181818</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-103pct.xlsx
+++ b/data/source/weekly/cs-en-us-103pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>15</v>
@@ -926,7 +926,7 @@
         <v>114.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>-31.818181818181</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>-18.181818181818</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>25</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="I16" s="14">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J16" s="14">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="K16" s="15">
-        <v>-1.052631578947</v>
+        <v>-10.280373831775</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.658119658119</v>
+        <v>-24.409448818897</v>
       </c>
       <c r="M16" s="15">
-        <v>-39.743589743589</v>
+        <v>-43.195266272189</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.386138613861</v>
+        <v>-82.320441988950</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D17" s="14">
         <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>52.941176470588</v>
       </c>
       <c r="F17" s="14">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G17" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H17" s="15">
-        <v>5.084745762711</v>
+        <v>24.590163934426</v>
       </c>
       <c r="I17" s="14">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="J17" s="14">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="K17" s="15">
-        <v>5.106382978723</v>
+        <v>8.730158730158</v>
       </c>
       <c r="L17" s="15">
-        <v>12.785388127853</v>
+        <v>13.223140495867</v>
       </c>
       <c r="M17" s="15">
-        <v>147</v>
+        <v>166.019417475728</v>
       </c>
       <c r="N17" s="15">
-        <v>-11.785714285714</v>
+        <v>-7.432432432432</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>30.769230769230</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
         <v>69</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K18" s="15">
-        <v>-2.816901408450</v>
+        <v>-10.389610389610</v>
       </c>
       <c r="L18" s="15">
         <v>23.214285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-17.857142857142</v>
+        <v>-22.471910112359</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.886426592797</v>
+        <v>-81.937172774869</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>46.153846153846</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>48.484848484848</v>
+        <v>55.263157894736</v>
       </c>
       <c r="I19" s="14">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="J19" s="14">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="K19" s="15">
-        <v>17.575757575757</v>
+        <v>20.224719101123</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.177033492822</v>
+        <v>-6.140350877192</v>
       </c>
       <c r="M19" s="15">
-        <v>56.451612903225</v>
+        <v>65.891472868217</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.510204081632</v>
+        <v>-47.931873479318</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>21.428571428571</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I20" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J20" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K20" s="15">
-        <v>7.692307692307</v>
+        <v>2.777777777777</v>
       </c>
       <c r="L20" s="15">
-        <v>-2.777777777777</v>
+        <v>-3.896103896103</v>
       </c>
       <c r="M20" s="15">
-        <v>12.903225806451</v>
+        <v>15.625</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.162895927601</v>
+        <v>-84.551148225469</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.122448979591</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="F21" s="17">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G21" s="17">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="H21" s="18">
-        <v>21.088435374149</v>
+        <v>18.562874251497</v>
       </c>
       <c r="I21" s="17">
-        <v>690</v>
+        <v>743</v>
       </c>
       <c r="J21" s="17">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="K21" s="18">
-        <v>6.811145510835</v>
+        <v>5.991440798858</v>
       </c>
       <c r="L21" s="18">
-        <v>1.173020527859</v>
+        <v>0.541271989174</v>
       </c>
       <c r="M21" s="18">
-        <v>28.491620111731</v>
+        <v>31.504424778761</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.705765407554</v>
+        <v>-65.377446411929</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>200</v>
       </c>
       <c r="F22" s="14">
+        <v>6</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
+        <v>15</v>
+      </c>
+      <c r="J22" s="14">
         <v>12</v>
       </c>
-      <c r="J22" s="14">
-        <v>11</v>
-      </c>
       <c r="K22" s="15">
-        <v>9.090909090909</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="L23" s="15">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>-6.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E24" s="15">
-        <v>32.142857142857</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="F24" s="14">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G24" s="14">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.068965517241</v>
+        <v>-21.348314606741</v>
       </c>
       <c r="I24" s="14">
-        <v>739</v>
+        <v>769</v>
       </c>
       <c r="J24" s="14">
-        <v>643</v>
+        <v>695</v>
       </c>
       <c r="K24" s="15">
-        <v>14.930015552099</v>
+        <v>10.647482014388</v>
       </c>
       <c r="L24" s="15">
-        <v>23.166666666666</v>
+        <v>21.484992101105</v>
       </c>
       <c r="M24" s="15">
-        <v>89.487179487179</v>
+        <v>86.650485436893</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E25" s="15">
-        <v>46.153846153846</v>
+        <v>-81.25</v>
       </c>
       <c r="F25" s="14">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G25" s="14">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="H25" s="15">
-        <v>16.455696202531</v>
+        <v>-26.213592233009</v>
       </c>
       <c r="I25" s="14">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="J25" s="14">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="K25" s="15">
-        <v>19.166666666666</v>
+        <v>10.714285714285</v>
       </c>
       <c r="L25" s="15">
-        <v>23.988439306358</v>
+        <v>17.615176151761</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>-36</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="F26" s="14">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G26" s="14">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.641975308641</v>
+        <v>-10.465116279069</v>
       </c>
       <c r="I26" s="14">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="J26" s="14">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="K26" s="15">
-        <v>15.302491103202</v>
+        <v>13.486842105263</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>2.071005917159</v>
       </c>
       <c r="M26" s="15">
-        <v>18.681318681318</v>
+        <v>21.052631578947</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,20 +1384,20 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>4</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
         <v>39</v>
       </c>
       <c r="J28" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="L28" s="15">
-        <v>8.333333333333</v>
+        <v>2.631578947368</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.617021276595</v>
+        <v>-96.078431372549</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.181818181818</v>
+        <v>-95.833333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>200</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
